--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Продукты" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Категории" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Справочник UZ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Бренды" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Продукты" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник UZ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бренды" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Продукты'!$A$1:$Y$168</definedName>
@@ -772,7 +772,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>183 товара · 12 брендов · 19 категорий</t>
+          <t>195 товаров · 13 брендов · 19 категорий</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE184"/>
+  <dimension ref="A1:AE196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.05"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9452,12 +9452,12 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>NOW Foods C-1000, 100 таблеток</t>
+          <t>NOW Foods C-1000 с шиповником, 100 таблеток</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>NOW Foods C-1000, 100 tabletka</t>
+          <t>NOW Foods C-1000 na'matak bilan, 100 tabletka</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -23202,6 +23202,1423 @@
         </is>
       </c>
       <c r="Y184" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>now-kids-liquid-echinacea</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>now-kids-liquid-echinacea-orange-59ml</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>NOW Kids Liquid Echinacea, апельсин, 59 мл</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NOW Kids Liquid Echinacea, apelsin, 59 ml</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Детские витамины</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Иммунитет</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Жидкость</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Жидкая эхинацея для детей без сахара и спирта, вкус апельсина.</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Bolalar uchun shakarsiz va spirtsiz suyuq exinatseya, apelsin ta'mi.</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>NOW Kids Liquid Echinacea — биологически активная добавка с экстрактом корня эхинацеи узколистной (Echinacea angustifolia) для детей, без сахара и спирта, с приятным апельсиновым вкусом. Помогает поддержать иммунитет ребёнка.</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>NOW Kids Liquid Echinacea — bolalar uchun moʻljallangan, tor bargli exinatseya (Echinacea angustifolia) ildizi ekstraktini saqlovchi, shakar va spirtsiz, yoqimli apelsin taʼmli biologik faol qoʻshimcha. Bolaning immunitetini qoʻllab-quvvatlashga yordam beradi.</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Экстракт корня эхинацеи узколистной (Echinacea angustifolia)</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Tor bargli exinatseya (Echinacea angustifolia) ildizi ekstrakti</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Перед использованием хорошо взболтать. Дозировку и продолжительность приёма уточните у педиатра.</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Ishlatishdan oldin yaxshilab chayqating. Doza va qabul muddatini pediatr bilan aniqlashtiring.</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Хранить в недоступном для детей месте. Перед применением проконсультируйтесь с педиатром.</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Bolalar yeta olmaydigan joyda saqlang. Qoʻllashdan oldin pediatr bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>images/now-kids-liquid-echinacea.jpg</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ecovita-liquid-chlorophyll</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ecovita-liquid-chlorophyll-mint-500ml</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ECOVITA Chlorophyll Liquid + Mentol, 500 мл</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ECOVITA Chlorophyll Liquid + Mentol, 500 ml</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Жидкость</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>50</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>1</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Жидкий хлорофилл с мятой — источник хлорофилла и меди, природная поддержка свежести дыхания.</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Yalpiz ta'mli suyuq xlorofill — xlorofill va mis manbai, nafas yangiligini tabiiy qo'llab-quvvatlash.</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>ECOVITA Жидкий хлорофилл — источник хлорофилла (в форме медного комплекса хлорофиллина натрия из экстракта листьев белой шелковицы) и меди, с натуральным мятным вкусом. Хлорофилл традиционно используется для поддержки внутренней свежести и как дополнительный источник антиоксидантов, а медь необходима для нормального обмена веществ.</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>ECOVITA Suyuq xlorofill — oq tut bargi ekstraktidan olingan natriy xlorofillin mis kompleksi shaklidagi xlorofill va mis manbai boʻlib, tabiiy yalpiz taʼmiga ega. Xlorofill anʼanaviy ravishda ichki yangilikni qoʻllab-quvvatlash va qoʻshimcha antioksidant manbai sifatida qoʻllaniladi, mis esa normal moddalar almashinuvi uchun zarur.</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Порция = 1 чайная ложка (5 мл): хлорофилл (медный комплекс хлорофиллина натрия из экстракта листьев белой шелковицы) — 50 мг; медь — 2,5 мг; вода очищенная, глицерин, сорбат калия, натуральный ароматизатор «ментол»</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Porsiya = 1 choy qoshiq (5 ml): xlorofill (oq tut bargi ekstraktidan olingan natriy xlorofillin mis kompleksi) — 50 mg; mis — 2,5 mg; tozalangan suv, glitserin, kaliy sorbati, tabiiy "mentol" aromatizatori</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 чайной ложке (5 мл), предварительно разведя в 100–150 мл воды или сока, 1 раз в день во время еды. Перед употреблением взболтать. Продолжительность приёма — 1 месяц, при необходимости курс можно повторить.</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — 1 choy qoshiq (5 ml) ni 100–150 ml suv yoki sharbatda eritib, kuniga 1 marta ovqat vaqtida iching. Ishlatishdan oldin chayqating. Qabul muddati — 1 oy, zarur boʻlsa kursni takrorlash mumkin.</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Индивидуальная непереносимость компонентов, беременность, кормление грудью. Не принимать одновременно с другими добавками, содержащими медь. Перед применением проконсультируйтесь с врачом. Хранить в сухом, защищённом от прямых солнечных лучей и недоступном для детей месте при температуре не выше +25°C. После вскрытия хранить в холодильнике не более 90 суток.</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Tarkibiy qismlarga individual toʻqnashmovchilik, homiladorlik, emizish davri. Boshqa mis saqlovchi qoʻshimchalar bilan bir vaqtda qabul qilmang. Qoʻllashdan oldin shifokor bilan maslahatlashing. Quruq, toʻgʻridan-toʻgʻri quyosh nuridan himoyalangan, bolalar yeta olmaydigan joyda, +25°C dan yuqori boʻlmagan haroratda saqlang. Ochilgandan keyin sovutgichda 90 kundan koʻp saqlamang.</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>images/ecovita-chlorophyll.jpg</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>solgar-calcium-magnesium-zinc</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>solgar-calcium-magnesium-zinc-250-tabs</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Solgar Calcium Magnesium plus Zinc, 250 таблеток</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Solgar Calcium Magnesium plus Zinc, 250 tabletka</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Таблетки</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>250</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Кальций, магний и цинк для здоровья костей, нервной системы и мышц.</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Suyaklar, asab tizimi va mushaklar salomatligi uchun kaltsiy, magniy va rux.</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Solgar Calcium Magnesium plus Zinc — комплекс для поддержки здоровья костей и зубов. Кальций служит строительным материалом костной ткани, магний помогает регулировать транспорт кальция и необходим для работы мышц и нервной системы, а цинк участвует в синтезе коллагена костной ткани. Подходит для веганов, не содержит глютена, пшеницы и молочных продуктов.</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Solgar Calcium Magnesium plus Zinc — suyak va tishlar salomatligini qoʻllab-quvvatlovchi kompleks. Kaltsiy suyak toʻqimasi uchun qurilish materiali boʻlib xizmat qiladi, magniy kaltsiy tashilishini boshqarishga yordam beradi va mushaklar hamda asab tizimi ishi uchun zarur, rux esa suyak toʻqimasida kollagen sintezida ishtirok etadi. Vegetarianlar uchun mos, glyutensiz, bugʻdoysiz va sut mahsulotlarisiz.</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>3 таблетки содержат: кальций (в виде карбоната, глюконата и цитрата кальция) — 1000 мг; магний (в виде оксида, глюконата и цитрата магния) — 400 мг; цинк (в виде глюконата цинка) — 15 мг; натрий (природного происхождения) — 15 мг; микрокристаллическая целлюлоза, растительная целлюлоза, лимонная кислота, стеарат магния (растительный), растительный глицерин, карнаубский воск</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>3 tabletka tarkibida: kaltsiy (kaltsiy karbonat, glyukonat va sitrat shaklida) — 1000 mg; magniy (magniy oksid, glyukonat va sitrat shaklida) — 400 mg; rux (rux glyukonat shaklida) — 15 mg; natriy (tabiiy kelib chiqishli) — 15 mg; mikrokristall sellyuloza, oʻsimlik sellyulozasi, limon kislotasi, magniy stearati (oʻsimlik), oʻsimlik glitserini, karnauba mumi</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Взрослым — по 3 таблетки в день во время еды; можно разделить на несколько приёмов в течение дня или принимать по рекомендации врача.</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — ovqat vaqtida kuniga 3 tabletka; kun davomida bir necha qabulga boʻlish yoki shifokor tavsiyasiga koʻra ichish mumkin.</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует.</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang.</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>images/solgar-calcium-magnesium-zinc.jpg</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>solgar-evening-primrose-oil</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>solgar-evening-primrose-oil-500mg-180-sgels</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Solgar Evening Primrose Oil 500 мг, 180 капсул</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Solgar Evening Primrose Oil 500 mg, 180 kapsula</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Красота: волосы, кожа, ногти</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Softgels</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>500</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>180</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Масло примулы вечерней холодного отжима — источник гамма-линоленовой кислоты (ГЛК).</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Sovuq presslangan kechki primula moyi — gamma-linolen kislotasi (GLK) manbai.</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Solgar Evening Primrose Oil — масло примулы вечерней холодного отжима, полученное без химических растворителей. Один из самых богатых источников гамма-линоленовой кислоты (ГЛК): помогает обеспечить питательную поддержку женщинам при ПМС, а также способствует здоровому состоянию кожи, нервной и сердечно-сосудистой систем.</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Solgar Evening Primrose Oil — kimyoviy erituvchilarsiz, sovuq presslash usulida olingan kechki primula moyi. Gamma-linolen kislotasi (GLK)ning eng boy manbalaridan biri: ayollarga PMS davrida oziqaviy yordam koʻrsatadi, shuningdek teri, asab va yurak-qon tomir tizimi salomatligiga koʻmaklashadi.</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: масло примулы вечерней (семена) — 500 мг; линолевая кислота — 365 мг; гамма-линоленовая кислота — 45 мг; желатин, растительный глицерин</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: kechki primula moyi (urugʻ) — 500 mg; linol kislotasi — 365 mg; gamma-linolen kislotasi — 45 mg; jelatin, oʻsimlik glitserini</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле 8 раз в день (желательно во время еды) или по рекомендации врача.</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 8 martagacha 1 tadan kapsula (afzalan ovqat vaqtida) yoki shifokor tavsiyasiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует. Перед применением проконсультируйтесь с врачом, если принимаете антикоагулянты или планируете операцию.</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Antikoagulyant qabul qilayotgan yoki jarrohlik amaliyotiga tayyorlanayotgan boʻlsangiz, qoʻllashdan oldin shifokor bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>images/solgar-evening-primrose-oil.jpg</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>solgar-gentle-iron</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>solgar-gentle-iron-25mg-90-vcaps</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Solgar Gentle Iron 25 мг, 90 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Solgar Gentle Iron 25 mg, 90 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Железо</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>25</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>90</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Бисглицинат железа — мягкая форма, не вызывает запоров и не раздражает желудок.</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Temir bisglitsinat — yumshoq shakl, qabziyat va oshqozon tirnashini keltirib chiqarmaydi.</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Solgar Gentle Iron — железо в форме бисглицината: усовершенствованная хелатная форма, которая хорошо переносится, не вызывает запоров и не раздражает желудок. Железо — важный компонент гемоглобина, переносящего кислород из лёгких ко всем тканям; поддерживает образование эритроцитов и использование энергии в организме. Не содержит пшеницы и молочных продуктов, подходит для веганов.</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Solgar Gentle Iron — temir bisglitsinat shaklida: yaxshi oʻzlashadigan, qabziyat keltirib chiqarmaydigan va oshqozonni tirnamaydigan takomillashtirilgan xelat shakl. Temir — kislorodni oʻpkadan barcha toʻqimalarga tashuvchi gemoglobinning muhim tarkibiy qismi; eritrotsitlar hosil boʻlishini va organizmda energiyadan foydalanishni qoʻllab-quvvatlaydi. Bugʻdoy va sut mahsulotlarisiz, vegetarianlar uchun mos.</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: железо (в виде бисглицината железа, хелат) — 25 мг; микрокристаллическая целлюлоза, растительная целлюлоза, стеарат магния (растительный)</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: temir (temir bisglitsinat, xelat shaklida) — 25 mg; mikrokristall sellyuloza, oʻsimlik sellyulozasi, magniy stearati (oʻsimlik)</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 растительной капсуле в день (желательно во время еды) или по рекомендации врача.</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 oʻsimlik kapsulasi (afzalan ovqat vaqtida) yoki shifokor tavsiyasiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует. Случайная передозировка препаратов железа — основная причина отравлений со смертельным исходом у детей до 6 лет; при передозировке немедленно обратитесь к врачу или в токсикологический центр.</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Temir preparatlarining tasodifiy ortiqcha dozasi 6 yoshgacha boʻlgan bolalarda oʻlimga olib keluvchi zaharlanishning asosiy sababidir; ortiqcha doza qabul qilinganda darhol shifokorga yoki toksikologiya markaziga murojaat qiling.</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>images/solgar-gentle-iron.jpg</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>solgar-collagen-hyaluronic</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>solgar-collagen-hyaluronic-acid-30-tabs</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Solgar Collagen Hyaluronic Acid Complex, 30 таблеток</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Solgar Collagen Hyaluronic Acid Complex, 30 tabletka</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Коллаген</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Красота: волосы, кожа, ногти</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Таблетки</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>30</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Комплекс BioCell Collagen II с гиалуроновой кислотой и витамином C для кожи и суставов.</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Teri va boʻgʻimlar uchun BioCell Collagen II, gialuron kislotasi va vitamin C kompleksi.</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Solgar Collagen Hyaluronic Acid Complex питает кожу изнутри: помогает поддерживать её эластичность и уменьшать заметность мелких и глубоких морщин, способствует выработке собственного коллагена. Содержит клинически изученный ингредиент BioCell Collagen II — матрицу пептидов коллагена II типа, хондроитинсульфата и гиалуроновой кислоты, а также витамин C, необходимый для образования коллагена и полезный для суставов.</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Solgar Collagen Hyaluronic Acid Complex terini ichkaridan oziqlantiradi: uning elastikligini saqlashga, mayda va chuqur ajinlarni kamroq sezilarli qilishga yordam beradi, oʻz kollagenining hosil boʻlishiga koʻmaklashadi. Tarkibida klinik oʻrganilgan BioCell Collagen II — II tur kollagen peptidlari, xondroitin sulfat va gialuron kislotasi matritsasi hamda kollagen hosil boʻlishi uchun zarur va boʻgʻimlar uchun foydali vitamin C bor.</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>1 таблетка содержит: витамин C (в виде аскорбата кальция) — 100 мг; натрий (природного происхождения) — 20 мг; BioCell Collagen II (гидролизованный экстракт куриного хряща) — 1200 мг; гидролизованный коллаген II типа — 720 мг; хондроитин сульфат — 192 мг; гиалуроновая кислота — 120 мг; микрокристаллическая целлюлоза, растительная целлюлоза, стеарат магния (растительный), фруктово-овощной сок и экстракт спирулины (красители), диоксид кремния, растительный глицерин, карнаубский воск</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>1 tabletka tarkibida: vitamin C (kaltsiy askorbat shaklida) — 100 mg; natriy (tabiiy kelib chiqishli) — 20 mg; BioCell Collagen II (tovuq togʻayi gidrolizlangan ekstrakti) — 1200 mg; gidrolizlangan II tur kollagen — 720 mg; xondroitin sulfat — 192 mg; gialuron kislotasi — 120 mg; mikrokristall sellyuloza, oʻsimlik sellyulozasi, magniy stearati (oʻsimlik), meva-sabzavot sharbati va spirulina ekstrakti (boʻyoqlar), kremniy dioksidi, oʻsimlik glitserini, karnauba mumi</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 таблетке в день, желательно во время еды, или по рекомендации врача.</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 tabletka, afzalan ovqat vaqtida, yoki shifokor tavsiyasiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует.</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang.</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>images/solgar-collagen-hyaluronic.jpg</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>solgar-skin-nails-hair</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>solgar-skin-nails-hair-60-tabs</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Solgar Skin, Nails &amp; Hair (MSM), 60 таблеток</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Solgar Skin, Nails &amp; Hair (MSM), 60 tabletka</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Красота: волосы, кожа, ногти</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Таблетки</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>60</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Комплекс с МСМ, витамином C, цинком и медью для красоты кожи, ногтей и волос.</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Teri, tirnoq va sochlar goʻzalligi uchun MSM, vitamin C, rux va misli kompleks.</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Solgar Skin, Nails &amp; Hair — формула для поддержки коллагена, основного компонента кожи, ногтей и волос, количество которого с возрастом снижается. Содержит МСМ (OptiMSM), витамин C, цинк, медь, кремний и аминокислоты L-пролин и L-лизин. Подходит для веганов, без глютена, пшеницы и молочных продуктов.</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Solgar Skin, Nails &amp; Hair — teri, tirnoq va sochlarning asosiy tarkibiy qismi boʻlgan, yosh oʻtgan sari kamayadigan kollagenni qoʻllab-quvvatlovchi formula. Tarkibida MSM (OptiMSM), vitamin C, rux, mis, kremniy hamda L-prolin va L-lizin aminokislotalari bor. Vegetarianlar uchun mos, glyutensiz, bugʻdoysiz va sut mahsulotlarisiz.</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>2 таблетки содержат: витамин C (в виде L-аскорбиновой кислоты) — 120 мг; цинк (в виде цитрата цинка) — 15 мг; медь (в виде глицината меди, хелат) — 2 мг; МСМ (метилсульфонилметан, OptiMSM) — 1000 мг; кремний — 50 мг; L-пролин — 50 мг; L-лизин (в виде гидрохлорида) — 50 мг; микрокристаллическая целлюлоза, растительная стеариновая кислота, растительная целлюлоза, стеарат магния (растительный), растительный глицерин</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>2 tabletka tarkibida: vitamin C (L-askorbin kislotasi shaklida) — 120 mg; rux (rux sitrat shaklida) — 15 mg; mis (mis glitsinat, xelat shaklida) — 2 mg; MSM (metilsulfonilmetan, OptiMSM) — 1000 mg; kremniy — 50 mg; L-prolin — 50 mg; L-lizin (gidroxlorid shaklida) — 50 mg; mikrokristall sellyuloza, oʻsimlik stearin kislotasi, oʻsimlik sellyulozasi, magniy stearati (oʻsimlik), oʻsimlik glitserini</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Взрослым — по 2 таблетки в день (желательно во время еды) или по рекомендации врача.</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 2 tabletka (afzalan ovqat vaqtida) yoki shifokor tavsiyasiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует.</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang.</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>images/solgar-skin-nails-hair.jpg</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>solgar-omega-3-950-50</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>solgar-omega-3-triple-strength-950mg-50-sgels</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 950 мг ЭПК и ДГК, 50 капсул</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 950 mg EPK va DGK, 50 kapsula</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Омега-3</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Softgels</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>950</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>50</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Рыбий жир тройной силы: 950 мг омега-3 (ЭПК и ДГК) в капсуле, очищен от ртути.</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Uch karra kuchli baliq yogʻi: kapsulada 950 mg omega-3 (EPK va DGK), simobdan tozalangan.</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 — самая высокая концентрация омега-3 кислот ЭПК и ДГК в линейке Solgar, полученных из холодноводной рыбы: 950 мг омега-3 в одной капсуле. Поддерживает здоровье сердечно-сосудистой системы, суставов и кожи. Проходит молекулярную дистилляцию для очистки от ртути; не содержит глютена, пшеницы и молочных продуктов.</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 — sovuq suvli baliqdan olingan EPK va DGK omega-3 kislotalarining Solgar qatoridagi eng yuqori konsentratsiyasi: bitta kapsulada 950 mg omega-3. Yurak-qon tomir tizimi, boʻgʻimlar va teri salomatligini qoʻllab-quvvatlaydi. Simobdan tozalash uchun molekulyar distillyatsiyadan oʻtadi; glyutensiz, bugʻdoysiz va sut mahsulotlarisiz.</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: омега-3 (всего, в виде этиловых эфиров) — 950 мг; ЭПК — 504 мг; ДГК — 378 мг; рыбий жир, желатин, растительный глицерин, натуральная смесь токоферолов; содержит рыбу (треска, сельдь, макрель, сардина)</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: omega-3 (jami, etil efirlar shaklida) — 950 mg; EPK — 504 mg; DGK — 378 mg; baliq yogʻi, jelatin, oʻsimlik glitserini, tabiiy tokoferollar aralashmasi; tarkibida baliq bor (treska, seld, skumbriya, sardina)</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле 2 раза в день (желательно во время еды) или по назначению врача.</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 2 marta 1 tadan kapsula (afzalan ovqat vaqtida) yoki shifokor tayinlashiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует. Перед применением проконсультируйтесь с врачом, если принимаете антикоагулянты или планируете операцию.</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Antikoagulyant qabul qilayotgan yoki jarrohlik amaliyotiga tayyorlanayotgan boʻlsangiz, qoʻllashdan oldin shifokor bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>images/solgar-omega-3-950-50.jpg</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>solgar-omega-3-950-100</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>solgar-omega-3-triple-strength-950mg-100-sgels</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 950 мг ЭПК и ДГК, 100 капсул</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 950 mg EPK va DGK, 100 kapsula</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Омега-3</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Softgels</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>950</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>100</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Рыбий жир тройной силы: 950 мг омега-3 (ЭПК и ДГК) в капсуле, очищен от ртути.</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Uch karra kuchli baliq yogʻi: kapsulada 950 mg omega-3 (EPK va DGK), simobdan tozalangan.</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 — самая высокая концентрация омега-3 кислот ЭПК и ДГК в линейке Solgar, полученных из холодноводной рыбы: 950 мг омега-3 в одной капсуле. Поддерживает здоровье сердечно-сосудистой системы, суставов и кожи. Проходит молекулярную дистилляцию для очистки от ртути; не содержит глютена, пшеницы и молочных продуктов.</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Solgar Triple Strength Omega-3 — sovuq suvli baliqdan olingan EPK va DGK omega-3 kislotalarining Solgar qatoridagi eng yuqori konsentratsiyasi: bitta kapsulada 950 mg omega-3. Yurak-qon tomir tizimi, boʻgʻimlar va teri salomatligini qoʻllab-quvvatlaydi. Simobdan tozalash uchun molekulyar distillyatsiyadan oʻtadi; glyutensiz, bugʻdoysiz va sut mahsulotlarisiz.</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: омега-3 (всего, в виде этиловых эфиров) — 950 мг; ЭПК — 504 мг; ДГК — 378 мг; рыбий жир, желатин, растительный глицерин, натуральная смесь токоферолов; содержит рыбу (треска, сельдь, макрель, сардина)</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: omega-3 (jami, etil efirlar shaklida) — 950 mg; EPK — 504 mg; DGK — 378 mg; baliq yogʻi, jelatin, oʻsimlik glitserini, tabiiy tokoferollar aralashmasi; tarkibida baliq bor (treska, seld, skumbriya, sardina)</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле 2 раза в день (желательно во время еды) или по назначению врача.</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 2 marta 1 tadan kapsula (afzalan ovqat vaqtida) yoki shifokor tayinlashiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует. Перед применением проконсультируйтесь с врачом, если принимаете антикоагулянты или планируете операцию.</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Antikoagulyant qabul qilayotgan yoki jarrohlik amaliyotiga tayyorlanayotgan boʻlsangiz, qoʻllashdan oldin shifokor bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>images/solgar-omega-3-950-100.jpg</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>solgar-selenium-100</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>solgar-selenium-100mcg-100-tabs</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Solgar Selenium 100 мкг, 100 таблеток</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Solgar Selenium 100 mkg, 100 tabletka</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Антиоксиданты</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Таблетки</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>100</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>мкг</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>100</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Бездрожжевой селен в форме L-селенометионина для антиоксидантной защиты и иммунитета.</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Antioksidant himoya va immunitet uchun L-selenometionin shaklidagi xamirturushsiz selen.</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Solgar Selenium — бездрожжевой селен в форме L-селенометионина. Селен — незаменимый микроэлемент, компонент антиоксидантного фермента глутатионпероксидазы: помогает бороться со свободными радикалами, поддерживает иммунную систему и участвует в переработке витамина E. Подходит для веганов, без глютена, пшеницы и молочных продуктов.</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Solgar Selenium — L-selenometionin shaklidagi xamirturushsiz selen. Selen — muhim mikroelement, glutationperoksidaza antioksidant fermentining tarkibiy qismi: erkin radikallarga qarshi kurashishga yordam beradi, immun tizimini qoʻllab-quvvatlaydi va E vitaminini qayta ishlashda ishtirok etadi. Vegetarianlar uchun mos, glyutensiz, bugʻdoysiz va sut mahsulotlarisiz.</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>1 таблетка содержит: селен (в виде L-селенометионина, без дрожжей) — 100 мкг; дикальция фосфат, микрокристаллическая целлюлоза, диоксид кремния, стеарат магния (растительный), растительная целлюлоза</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>1 tabletka tarkibida: selen (L-selenometionin shaklida, xamirturushsiz) — 100 mkg; dikaltsiy fosfat, mikrokristall sellyuloza, kremniy dioksidi, magniy stearati (oʻsimlik), oʻsimlik sellyulozasi</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 таблетке 1–2 раза в день (желательно во время еды) или по назначению врача.</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1–2 marta 1 tadan tabletka (afzalan ovqat vaqtida) yoki shifokor tayinlashiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует.</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang.</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>images/solgar-selenium-100.jpg</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>solgar-vitamin-k2-100</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>solgar-vitamin-k2-100mcg-50-vcaps</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Solgar Naturally Sourced Vitamin K2 (MK-7) 100 мкг, 50 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Solgar Naturally Sourced Vitamin K2 (MK-7) 100 mkg, 50 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Витамины</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>100</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>мкг</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>50</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Натуральный витамин K2 (MK-7) из экстракта натто для здоровья костей.</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Suyaklar salomatligi uchun natto ekstraktidan olingan tabiiy K2 vitamini (MK-7).</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Solgar Naturally Sourced Vitamin K2 — активная форма витамина K (менахинон-7, MK-7), важная для здоровья костей. Витамин K2 не поступает с пищей в доступной организму форме; в этой добавке он получен из экстракта натто — ферментированного соевого продукта, природного источника MK-7. Подходит для лактовегетарианцев, без глютена, пшеницы и ГМО.</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Solgar Naturally Sourced Vitamin K2 — suyaklar salomatligi uchun muhim boʻlgan K vitaminining faol shakli (menaxinon-7, MK-7). K2 vitamini ovqat bilan organizm oʻzlashtira oladigan shaklda tushmaydi; bu qoʻshimchada u natto — fermentlangan soya mahsuloti, MK-7 ning tabiiy manbai ekstraktidan olingan. Laktovegetarianlar uchun mos, glyutensiz, bugʻdoysiz va GMOsiz.</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: витамин K2 (в виде менахинона-7, MK-7 из экстракта натто) — 100 мкг; кальций — 115 мг; дикальция фосфат, растительная целлюлоза, стеарат магния (растительный), диоксид кремния; содержит молоко и сою</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: vitamin K2 (menaxinon-7, natto ekstraktidan MK-7 shaklida) — 100 mkg; kaltsiy — 115 mg; dikaltsiy fosfat, oʻsimlik sellyulozasi, magniy stearati (oʻsimlik), kremniy dioksidi; tarkibida sut va soya bor</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 растительной капсуле в день (желательно во время еды) или по рекомендации врача.</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 oʻsimlik kapsulasi (afzalan ovqat vaqtida) yoki shifokor tavsiyasiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует. Все формы витамина K могут взаимодействовать с препаратами, разжижающими кровь — при их приёме проконсультируйтесь с врачом.</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. K vitaminining barcha shakllari qonni suyultiruvchi dorilar bilan oʻzaro taʼsirlashishi mumkin — ularni qabul qilayotgan boʻlsangiz, shifokor bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>images/solgar-vitamin-k2-100.jpg</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>solgar-zinc-picolinate-22</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>solgar-zinc-picolinate-22mg-100-tabs</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Solgar Zinc Picolinate 22 мг, 100 таблеток</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Solgar Zinc Picolinate 22 mg, 100 tabletka</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Иммунитет</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Таблетки</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>22</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>100</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Цинк в форме пиколината для кожи, иммунитета и антиоксидантной защиты.</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Teri, immunitet va antioksidant himoya uchun pikolinat shaklidagi rux.</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Solgar Zinc Picolinate — цинк высшего качества в форме пиколината. Цинк способствует здоровью кожи, поддерживает в норме вкусовые рецепторы и зрение, обладает антиоксидантным действием и может поддерживать иммунную систему. Подходит для веганов, без глютена, пшеницы и молочных продуктов.</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Solgar Zinc Picolinate — pikolinat shaklidagi yuqori sifatli rux. Rux teri salomatligiga koʻmaklashadi, taʼm sezish va koʻrishni me’yorda saqlaydi, antioksidant taʼsirga ega va immun tizimini qoʻllab-quvvatlashi mumkin. Vegetarianlar uchun mos, glyutensiz, bugʻdoysiz va sut mahsulotlarisiz.</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>1 таблетка содержит: цинк (в виде пиколината цинка) — 22 мг; дикальция фосфат, микрокристаллическая целлюлоза, стеариновая кислота (растительная), целлюлоза (растительная), стеарат магния (растительный)</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>1 tabletka tarkibida: rux (rux pikolinat shaklida) — 22 mg; dikaltsiy fosfat, mikrokristall sellyuloza, stearin kislotasi (oʻsimlik), sellyuloza (oʻsimlik), magniy stearati (oʻsimlik)</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 таблетке в день, желательно во время еды, или по рекомендации врача.</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 tabletka, afzalan ovqat vaqtida, yoki shifokor tavsiyasiga koʻra.</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Перед применением при беременности, кормлении грудью, приёме лекарств или наличии заболеваний проконсультируйтесь с врачом. При появлении нежелательных реакций прекратите приём и обратитесь к врачу. Хранить в недоступном для детей месте при комнатной температуре. Не использовать, если защитная плёнка повреждена или отсутствует.</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Homiladorlik, emizish davrida, dori qabul qilayotganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Nojoʻya taʼsirlar yuzaga kelsa, qabulni toʻxtatib, shifokorga murojaat qiling. Bolalar yeta olmaydigan joyda, xona haroratida saqlang. Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang.</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>images/solgar-zinc-picolinate-22.jpg</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
         <is>
           <t>опубликован</t>
         </is>
@@ -23842,7 +25259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.05"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -23981,6 +25398,16 @@
         <v>13</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Solgar</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -772,7 +772,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>195 товаров · 13 брендов · 19 категорий</t>
+          <t>209 товаров · 13 брендов · 19 категорий</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE196"/>
+  <dimension ref="A1:AE210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.05"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24619,6 +24619,1708 @@
         </is>
       </c>
       <c r="Y196" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>solaray-vitamin-c-500</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>solaray-buffered-vitamin-c-bioflavonoids-500mg-100-vegcaps</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Solaray Buffered Vitamin C с биофлавоноидами 500 мг, 100 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Solaray Buffered Vitamin C bioflavonoidlar bilan 500 mg, 100 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Витамины</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Иммунитет</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>500</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>100</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Забуференный витамин C 500 мг с биофлавоноидным концентратом для иммунитета.</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Immunitet uchun bioflavonoid konsentratli buferlangan vitamin C 500 mg.</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Solaray Buffered Vitamin C — витамин C в забуференной (мягкой для желудка) форме с биофлавоноидным концентратом из лимона, рутином, гесперидином и основой из шиповника и ацеролы. Укрепляет иммунитет и работает как антиоксидант. Веганский продукт, подтверждена эффективность лабораторными исследованиями.</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Solaray Buffered Vitamin C — limondan olingan bioflavonoid konsentrati, rutin, gesperidin hamda na’matak va asserola asosi bilan buferlangan (oshqozon uchun yumshoq) shakldagi vitamin C. Immunitetni mustahkamlaydi va antioksidant sifatida ishlaydi. Vegan mahsulot, samaradorligi laboratoriya tadqiqotlari bilan tasdiqlangan.</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: витамин C (аскорбиновая кислота) — 500 мг; кальций (карбонат кальция) — 20 мг; магний (оксид магния) — 37 мг; основа для поддержки витамина C (шиповник, ацерола) — 95 мг; концентрат биофлавоноидов (из лимона) — 100 мг; концентрат рутина — 50 мг; концентрат гесперидина — 25 мг; капсула из растительной целлюлозы, стеарат магния, акация</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: vitamin C (askorbin kislotasi) — 500 mg; kaltsiy (kaltsiy karbonat) — 20 mg; magniy (magniy oksid) — 37 mg; vitamin C ni qoʻllab-quvvatlovchi asos (na’matak, asserola) — 95 mg; bioflavonoidlar konsentrati (limondan) — 100 mg; rutin konsentrati — 50 mg; gesperidin konsentrati — 25 mg; oʻsimlik sellyulozasi kapsulasi, magniy stearati, akatsiya</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 растительной капсуле в день во время еды или запивая стаканом воды.</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 oʻsimlik kapsulasi, ovqat vaqtida yoki bir stakan suv bilan.</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Не использовать, если защитная плёнка повреждена или отсутствует. Хранить в недоступном для детей месте, в сухом и прохладном месте. Перед началом применения проконсультируйтесь с врачом.</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Bolalar yeta olmaydigan, quruq va salqin joyda saqlang. Qoʻllashdan oldin shifokor bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>images/solaray-vitamin-c-buffered-500.jpg</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>solaray-chromium-500</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>solaray-chromium-picolinate-500mcg-60-tabs</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Solaray Chromium Picolinate 500 мкг, 60 таблеток</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Solaray Chromium Picolinate 500 mkg, 60 tabletka</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Таблетки</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>500</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>мкг</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>60</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Пиколинат хрома 500 мкг для поддержки здорового уровня глюкозы в крови.</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Qondagi glyukoza darajasini sogʻlom saqlash uchun xrom pikolinat 500 mkg.</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Solaray Chromium Picolinate — хром в предпочтительной трёхвалентной форме (пиколинат). Предназначен для питательной поддержки здорового уровня глюкозы в крови. Эффективность подтверждена результатами лабораторных исследований.</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Solaray Chromium Picolinate — afzal koʻriladigan uch valentli shakldagi (pikolinat) xrom. Qondagi glyukoza darajasini sogʻlom saqlashga oziqaviy yordam berish uchun moʻljallangan. Samaradorligi laboratoriya tadqiqotlari bilan tasdiqlangan.</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>1 таблетка содержит: хром (из пиколината хрома) — 500 мкг; целлюлоза, стеариновая кислота, кроскармеллоза натрия, стеарат магния</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>1 tabletka tarkibida: xrom (xrom pikolinatdan) — 500 mkg; sellyuloza, stearin kislotasi, natriy kroskarmelloza, magniy stearati</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 таблетке в день во время еды или запивая стаканом воды.</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 tabletka, ovqat vaqtida yoki bir stakan suv bilan.</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Не использовать, если защитная плёнка повреждена или отсутствует. Хранить в недоступном для детей месте, в сухом и прохладном месте. Перед началом применения проконсультируйтесь с врачом.</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Bolalar yeta olmaydigan, quruq va salqin joyda saqlang. Qoʻllashdan oldin shifokor bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>images/solaray-chromium-picolinate-500.jpg</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>solaray-selenium-200-100</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>solaray-high-potency-selenium-200mcg-100-vegcaps</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Solaray High Potency Selenium 200 мкг, 100 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Solaray High Potency Selenium 200 mkg, 100 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Антиоксиданты</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>200</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>мкг</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>100</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Высокоэффективный селен 200 мкг из селеновых дрожжей — антиоксидантная защита.</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Selenli xamirturushdan olingan yuqori samarali selen 200 mkg — antioksidant himoya.</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Solaray High Potency Selenium — селен из органически связанных селеновых дрожжей. Незаменимый микроэлемент, обеспечивающий антиоксидантную защиту. Эффективность подтверждена результатами лабораторных исследований.</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Solaray High Potency Selenium — organik bogʻlangan selenli xamirturushdan olingan selen. Antioksidant himoyani taʼminlovchi muhim mikroelement. Samaradorligi laboratoriya tadqiqotlari bilan tasdiqlangan.</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: селен (из органически связанных селеновых дрожжей) — 200 мкг; пищевые дрожжи, растительная целлюлоза (капсула), стеарат магния</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: selen (organik bogʻlangan selenli xamirturushdan) — 200 mkg; oziq-ovqat xamirturushi, oʻsimlik sellyulozasi (kapsula), magniy stearati</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 вегетарианской капсуле в день во время еды или запивая стаканом воды.</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 vegetarian kapsula, ovqat vaqtida yoki bir stakan suv bilan.</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Хранить плотно закрытым в прохладном, сухом месте, в недоступном для детей месте. Содержит дрожжи.</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Zich yopilgan holda, salqin va quruq, bolalar yeta olmaydigan joyda saqlang. Tarkibida xamirturush bor.</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>images/solaray-high-potency-selenium-200.jpg</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>solaray-zinc-50</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>solaray-zinc-50mg-100-vegcaps</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Solaray Zinc 50 мг, 100 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Solaray Zinc 50 mg, 100 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Иммунитет</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>50</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>100</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Аминокислотный хелат цинка 50 мг для иммунитета, кожи и работы клеток.</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Immunitet, teri va hujayralar ishi uchun aminokislotali rux xelati 50 mg.</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Solaray Zinc — 50 мг цинка в виде аминокислотного хелата для лучшего усвоения. Цинк участвует более чем в 100 ферментативных реакциях, необходим для иммунной системы, здоровья кожи и работы клеток и не накапливается в организме. Веганский продукт.</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Solaray Zinc — yaxshi oʻzlashishi uchun aminokislotali xelat shaklidagi 50 mg rux. Rux 100 dan ortiq fermentativ reaksiyada ishtirok etadi, immun tizimi, teri salomatligi va hujayralar ishi uchun zarur va organizmda toʻplanmaydi. Vegan mahsulot.</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: цинк (из комплекса аминокислотного хелата цинка) — 50 мг; семена тыквы (Cucurbita pepo) — 50 мг; концентрат цельного риса, капсула из растительной целлюлозы, целлюлоза, смесь экстрактов органического риса, диоксид кремния</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: rux (rux aminokislotali xelat kompleksidan) — 50 mg; qovoq (Cucurbita pepo) urugʻi — 50 mg; butun guruch konsentrati, oʻsimlik sellyulozasi kapsulasi, sellyuloza, organik guruch ekstraktlari aralashmasi, kremniy dioksidi</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 растительной капсуле в день во время еды или запивая стаканом воды.</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 oʻsimlik kapsulasi, ovqat vaqtida yoki bir stakan suv bilan.</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Не использовать, если защитная плёнка повреждена или отсутствует. Хранить в недоступном для детей месте, в сухом и прохладном месте. Перед началом применения проконсультируйтесь с врачом. Длительное применение может повлиять на статус меди — возможно, потребуется дополнительный приём меди.</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Bolalar yeta olmaydigan, quruq va salqin joyda saqlang. Qoʻllashdan oldin shifokor bilan maslahatlashing. Uzoq muddat qabul qilish mis holatiga taʼsir qilishi mumkin — qoʻshimcha mis qabul qilish zarur boʻlishi mumkin.</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>images/solaray-zinc-50.jpg</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>solaray-iron-50</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>solaray-iron-50mg-60-vegcaps</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Solaray Iron 50 мг, 60 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Solaray Iron 50 mg, 60 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Железо</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>50</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>60</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Аминокислотный хелат железа 50 мг — усвояемая форма для кровообращения.</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Qon aylanishi uchun yaxshi oʻzlashadigan aminokislotali temir xelati 50 mg.</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Solaray Iron — железо, вступившее в реакцию с аспарагиновой кислотой, концентратом цельного риса и лимонной кислотой для создания более усваиваемого хелатного комплекса. Железо — жизненно важная часть красных кровяных телец; поддерживает кровообращение и здоровье сердечно-сосудистой системы.</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Solaray Iron — aspartik kislota, butun guruch konsentrati va limon kislotasi bilan reaksiyaga kirishib, yaxshiroq oʻzlashadigan xelat kompleksi hosil qilgan temir. Temir — qizil qon tanachalarining muhim qismi; qon aylanishi va yurak-qon tomir tizimi salomatligini qoʻllab-quvvatlaydi.</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: железо (из комплекса аминокислотного хелата железа) — 50 мг; травяная основа (листья петрушки, рисовая мука, корень щавеля), капсула из растительной целлюлозы, аскорбил пальмитат</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: temir (temirning aminokislotali xelat kompleksidan) — 50 mg; oʻsimlik asosi (petrushka bargi, guruch uni, shovul ildizi), oʻsimlik sellyulozasi kapsulasi, askorbil palmitat</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 растительной капсуле в день во время еды или запивая стаканом воды.</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 oʻsimlik kapsulasi, ovqat vaqtida yoki bir stakan suv bilan.</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Не использовать, если защитная плёнка повреждена или отсутствует. Хранить в недоступном для детей месте, в сухом и прохладном месте. Перед началом применения проконсультируйтесь с врачом. Не предназначено для лиц младше 18 лет. Случайная передозировка препаратов железа — основная причина отравлений со смертельным исходом у детей до 6 лет; при передозировке немедленно обратитесь к врачу или в токсикологический центр.</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Bolalar yeta olmaydigan, quruq va salqin joyda saqlang. Qoʻllashdan oldin shifokor bilan maslahatlashing. 18 yoshgacha boʻlganlar uchun moʻljallanmagan. Temir preparatlarining tasodifiy ortiqcha dozasi 6 yoshgacha boʻlgan bolalarda oʻlimga olib keluvchi zaharlanishning asosiy sababidir; ortiqcha doza qabul qilinganda darhol shifokorga yoki toksikologiya markaziga murojaat qiling.</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>images/solaray-iron-50.jpg</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>solaray-inositol-500</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>solaray-inositol-500mg-100-vegcaps</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Solaray Inositol 500 мг, 100 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Solaray Inositol 500 mg, 100 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Витамины</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Нервная система и сон</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>500</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>100</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Инозитол 500 мг для здоровья на клеточном уровне.</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Hujayra darajasidagi salomatlik uchun inozitol 500 mg.</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Solaray Inositol — инозитол, питательное вещество, которое вырабатывается в организме, а также содержится в растениях и продуктах животного происхождения. Обеспечивает питательную поддержку клеточного здоровья и хорошего самочувствия. Вегетарианский продукт.</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Solaray Inositol — organizmda ishlab chiqariladigan hamda oʻsimlik va hayvon mahsulotlarida uchraydigan oziq modda inozitol. Hujayra salomatligi va yaxshi kayfiyatga oziqaviy yordam beradi. Vegetarian mahsulot.</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: инозитол — 500 мг; капсула из растительной целлюлозы, концентрат цельного риса, экстракт органических рисовых отрубей, диоксид кремния</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: inozitol — 500 mg; oʻsimlik sellyulozasi kapsulasi, butun guruch konsentrati, organik guruch kepagi ekstrakti, kremniy dioksidi</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле в день во время еды или запивая стаканом воды.</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 kapsula, ovqat vaqtida yoki bir stakan suv bilan.</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Не использовать, если защитная плёнка повреждена или отсутствует. Хранить в недоступном для детей месте, в сухом и прохладном месте. Перед началом применения проконсультируйтесь с врачом.</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Bolalar yeta olmaydigan, quruq va salqin joyda saqlang. Qoʻllashdan oldin shifokor bilan maslahatlashing.</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>images/solaray-inositol-500.jpg</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>solaray-tongkat-ali-400</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>solaray-tongkat-ali-400mg-60-vegcaps</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Solaray Tongkat Ali (Эврикома длиннолистная) 400 мг, 60 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Solaray Tongkat Ali (Eurycoma longifolia) 400 mg, 60 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Травы и экстракты</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>400</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>60</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Корень эврикомы длиннолистной (тонгкат али) 400 мг — растительная поддержка.</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Uzun bargli evrikoma ildizi (tongkat ali) 400 mg — oʻsimlik asosidagi yordam.</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Solaray Tongkat Ali — корень эврикомы длиннолистной (Eurycoma longifolia), тропического растения из джунглей Индонезии, Малайзии и Вьетнама, который традиционно используется для растительной поддержки организма. Веганский продукт, сертификат Non-GMO Project Verified.</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Solaray Tongkat Ali — Indoneziya, Malayziya va Vetnam oʻrmonlarida oʻsadigan tropik oʻsimlik — uzun bargli evrikoma (Eurycoma longifolia) ildizi; organizmni oʻsimlik asosida qoʻllab-quvvatlash uchun anʼanaviy ravishda ishlatiladi. Vegan mahsulot, Non-GMO Project Verified sertifikati.</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: корень эврикомы длиннолистной (Eurycoma longifolia) — 400 мг; капсула из растительной целлюлозы, целлюлоза, стеарат магния, экстракт рисовых отрубей, диоксид кремния</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: uzun bargli evrikoma (Eurycoma longifolia) ildizi — 400 mg; oʻsimlik sellyulozasi kapsulasi, sellyuloza, magniy stearati, guruch kepagi ekstrakti, kremniy dioksidi</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 растительной капсуле 2 раза в день во время еды или запивая стаканом воды.</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 2 marta 1 tadan oʻsimlik kapsulasi, ovqat vaqtida yoki bir stakan suv bilan.</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Не использовать, если защитная плёнка повреждена или отсутствует. Хранить в недоступном для детей месте, в сухом и прохладном месте. Перед началом применения проконсультируйтесь с врачом. Не принимать при беременности и кормлении грудью.</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Himoya pardasi shikastlangan yoki yoʻq boʻlsa, ishlatmang. Bolalar yeta olmaydigan, quruq va salqin joyda saqlang. Qoʻllashdan oldin shifokor bilan maslahatlashing. Homiladorlik va emizish davrida qabul qilmang.</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Solaray</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>images/solaray-tongkat-ali-400.jpg</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>now-nac-600-selenium</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>now-nac-600mg-selenium-100-caps</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>NOW Foods NAC 600 мг с селеном, 100 капсул</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NOW Foods NAC 600 mg selen bilan, 100 kapsula</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Аминокислоты</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Антиоксиданты</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>600</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>100</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>N-ацетилцистеин 600 мг с селеном — защита от свободных радикалов и здоровье клеток.</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Selenli N-asetilsisteyin 600 mg — erkin radikallardan himoya va hujayra salomatligi.</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>NOW NAC — N-ацетилцистеин, стабильная форма заменимой аминокислоты цистеина, необходимой для образования глутатиона. В формулу добавлен селен — микроэлемент, участвующий в выработке важных ферментов. Защищает от свободных радикалов и поддерживает здоровье клеток. Без ГМО, кошерный и халяльный продукт.</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>NOW NAC — N-asetilsisteyin, glutation hosil boʻlishi uchun zarur boʻlgan almashinadigan aminokislota sisteinning barqaror shakli. Formulaga muhim fermentlar ishlab chiqarilishida ishtirok etuvchi mikroelement selen qoʻshilgan. Erkin radikallardan himoya qiladi va hujayra salomatligini qoʻllab-quvvatlaydi. GMOsiz, koshir va halol mahsulot.</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: селен (элементарный, из L-селенометионина) — 25 мкг; N-ацетилцистеин (NAC) — 600 мг; гипромеллоза (целлюлозная капсула), стеариновая кислота (растительная), лимонная кислота, микрокристаллическая целлюлоза</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: selen (elementar, L-selenometionindan) — 25 mkg; N-asetilsisteyin (NAC) — 600 mg; gipromelloza (sellyuloza kapsulasi), stearin kislotasi (oʻsimlik), limon kislotasi, mikrokristall sellyuloza</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле 2 раза в день.</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 2 marta 1 tadan kapsula.</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Только для взрослых. Если вы беременны, кормите грудью, принимаете лекарства или у вас есть заболевания, проконсультируйтесь с врачом. Хранить в недоступном для детей месте. После вскрытия хранить в сухом и прохладном месте. Продукт может естественным образом менять цвет. На капсулах могут появиться крапинки — это не влияет на качество.</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Faqat kattalar uchun. Homilador boʻlsangiz, emizayotgan boʻlsangiz, dori qabul qilsangiz yoki kasalligingiz boʻlsa, shifokor bilan maslahatlashing. Bolalar yeta olmaydigan joyda saqlang. Ochilgandan keyin quruq va salqin joyda saqlang. Mahsulot tabiiy ravishda rangini oʻzgartirishi mumkin. Kapsulalarda dogʻlar paydo boʻlishi mumkin — bu sifatga taʼsir qilmaydi.</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>images/now-nac-600-selenium.jpg</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>now-nac-1000</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>now-nac-1000mg-60-tabs</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>NOW Foods NAC 1000 мг, 60 таблеток</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NOW Foods NAC 1000 mg, 60 tabletka</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Аминокислоты</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Пищеварение и печень</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Таблетки</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>60</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>N-ацетилцистеин 1000 мг — защита от свободных радикалов, иммунитет и здоровье печени.</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>N-asetilsisteyin 1000 mg — erkin radikallardan himoya, immunitet va jigar salomatligi.</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>NOW NAC 1000 — N-ацетилцистеин, стабильная форма аминокислоты цистеина, поддерживающая образование глутатиона — мощного соединения, нейтрализующего свободные радикалы. Поддерживает иммунную систему и здоровье печени. Подходит для вегетарианцев и веганов, без ГМО.</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>NOW NAC 1000 — sisteyin aminokislotasining barqaror shakli boʻlgan N-asetilsisteyin; erkin radikallarni zararsizlantiruvchi kuchli birikma — glutation hosil boʻlishini qoʻllab-quvvatlaydi. Immun tizimi va jigar salomatligini qoʻllab-quvvatlaydi. Vegetarianlar va veganlar uchun mos, GMOsiz.</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>1 таблетка содержит: N-ацетилцистеин (NAC) — 1000 мг; микрокристаллическая целлюлоза, гидроксипропилцеллюлоза, стеариновая кислота (растительная), кроскармеллоза натрия, оболочка (гипромеллоза, лецитин подсолнечника, триэтилцитрат), диоксид кремния</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>1 tabletka tarkibida: N-asetilsisteyin (NAC) — 1000 mg; mikrokristall sellyuloza, gidroksipropilsellyuloza, stearin kislotasi (oʻsimlik), natriy kroskarmelloza, qobiq (gipromelloza, kungaboqar lesitini, trietilsitrat), kremniy dioksidi</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 таблетке 1–3 раза в день.</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1–3 marta 1 tadan tabletka.</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Только для взрослых. Перед применением при беременности, кормлении грудью, приёме лекарств (особенно нитроглицерина) или наличии заболеваний проконсультируйтесь с врачом. Хранить в недоступном для детей месте. После вскрытия хранить в сухом и прохладном месте. Продукт может естественным образом менять цвет.</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Faqat kattalar uchun. Homiladorlik, emizish davrida, dori (ayniqsa nitrogliserin) qabul qilganda yoki kasallik mavjud boʻlganda qoʻllashdan oldin shifokor bilan maslahatlashing. Bolalar yeta olmaydigan joyda saqlang. Ochilgandan keyin quruq va salqin joyda saqlang. Mahsulot tabiiy ravishda rangini oʻzgartirishi mumkin.</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>images/now-nac-1000.jpg</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>now-coq10-100-hawthorn</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>now-coq10-100mg-hawthorn-30-vcaps</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>NOW Foods CoQ10 100 мг с боярышником, 30 растительных капсул</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NOW Foods CoQ10 100 mg andoʻz bilan, 30 oʻsimlik kapsulasi</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Антиоксиданты</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>100</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>30</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Коэнзим Q10 100 мг с ягодами боярышника для сердца и выработки клеточной энергии.</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Yurak va hujayra energiyasi ishlab chiqarilishi uchun andoʻz mevali koenzim Q10 100 mg.</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>NOW CoQ10 — коэнзим Q10, витаминоподобное соединение, играющее ключевую роль в выработке клеточной энергии. Больше всего его в сердце, печени и почках, а с возрастом собственная выработка снижается. В формулу добавлены ягоды боярышника. Поддерживает здоровье сердечно-сосудистой системы. Для вегетарианцев и веганов, сертификат Non-GMO Project Verified.</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>NOW CoQ10 — hujayra energiyasi ishlab chiqarilishida muhim rol oʻynaydigan vitaminga oʻxshash birikma — koenzim Q10. Eng koʻp yurak, jigar va buyraklarda boʻladi, yosh oʻtgan sari oʻz ishlab chiqarilishi kamayadi. Formulaga andoʻz mevalari qoʻshilgan. Yurak-qon tomir tizimi salomatligini qoʻllab-quvvatlaydi. Vegetarianlar va veganlar uchun, Non-GMO Project Verified sertifikati.</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: коэнзим Q10 (CoQ10) — 100 мг; ягоды боярышника (Crataegus laevigata и/или monogyna) — 400 мг; гипромеллоза (целлюлозная капсула)</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: koenzim Q10 (CoQ10) — 100 mg; andoʻz mevalari (Crataegus laevigata va/yoki monogyna) — 400 mg; gipromelloza (sellyuloza kapsulasi)</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле в день во время приёма жиросодержащей пищи.</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 kapsula, yogʻli ovqat bilan birga.</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Только для взрослых. Если вы беременны, кормите грудью, принимаете лекарства или у вас есть заболевания, проконсультируйтесь с врачом. Хранить в недоступном для детей месте. После вскрытия хранить в сухом и прохладном месте. Продукт может естественным образом менять цвет.</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Faqat kattalar uchun. Homilador boʻlsangiz, emizayotgan boʻlsangiz, dori qabul qilsangiz yoki kasalligingiz boʻlsa, shifokor bilan maslahatlashing. Bolalar yeta olmaydigan joyda saqlang. Ochilgandan keyin quruq va salqin joyda saqlang. Mahsulot tabiiy ravishda rangini oʻzgartirishi mumkin.</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>images/now-coq10-100-hawthorn.jpg</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ecovita-magnesium-glycinate-360</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ecovita-magnesium-glycinate-360mg-120</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Glycinate 360 мг, 120 капсул</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Glycinate 360 mg, 120 kapsula</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Нервная система и сон</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>360</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>120</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Магний в форме бисглицината — снижает мышечное напряжение, поддерживает нервную систему и отдых.</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Bisglitsinat shaklidagi magniy — mushaklar zoʻriqishini kamaytiradi, asab tizimi va dam olishni qoʻllab-quvvatlaydi.</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Glycinate (магний хелат усиленный) — магний в виде бисглицината, хорошо усваиваемой хелатной формы. Помогает снижать мышечное напряжение, поддерживает здоровье нервной системы и способствует полноценному отдыху. Дополнительный источник магния. Халяль.</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Glycinate (kuchaytirilgan magniy xelat) — yaxshi oʻzlashadigan xelat shakli boʻlgan bisglitsinat koʻrinishidagi magniy. Mushaklar zoʻriqishini kamaytirishga, asab tizimi salomatligini qoʻllab-quvvatlashga va toʻliq dam olishga yordam beradi. Magniyning qoʻshimcha manbai. Halol.</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>3 капсулы содержат: магния бисглицинат — 1800 мг; элементарный магний — 360 мг; микрокристаллическая целлюлоза (носитель), диоксид кремния (антислеживатель), капсула (желатин или гидроксипропилметилцеллюлоза)</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>3 kapsula tarkibida: magniy bisglitsinat — 1800 mg; elementar magniy — 360 mg; mikrokristall sellyuloza (tashuvchi), kremniy dioksidi (qotib qolishga qarshi), kapsula (jelatin yoki gidroksipropilmetilsellyuloza)</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Взрослым — по 3–4 капсулы в день во время приёма пищи. Продолжительность приёма — 1 месяц, при необходимости курс можно повторить.</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 3–4 kapsula, ovqat vaqtida. Qabul muddati — 1 oy, zarur boʻlsa kursni takrorlash mumkin.</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Индивидуальная непереносимость компонентов, беременность, период лактации, возраст до 18 лет. Перед применением проконсультируйтесь с врачом. Хранить в сухом, прохладном, защищённом от прямых солнечных лучей и недоступном для детей месте при температуре не выше 25°C и относительной влажности не более 75%, в закрытой неповреждённой упаковке. Срок годности — 2 года.</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Tarkibiy qismlarga individual toʻqnashmovchilik, homiladorlik, laktatsiya davri, 18 yoshgacha. Qoʻllashdan oldin shifokor bilan maslahatlashing. Quruq, salqin, toʻgʻridan-toʻgʻri quyosh nuridan himoyalangan, bolalar yeta olmaydigan joyda, 25°C dan yuqori boʻlmagan haroratda va nisbiy namlik 75% dan oshmagan sharoitda, yopiq butun qadoqda saqlang. Yaroqlilik muddati — 2 yil.</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>images/ecovita-magnesium-glycinate-360.jpg</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ecovita-magnesium-malate-200</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ecovita-magnesium-malate-200mg-60</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Malate 200 мг, 60 капсул</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Malate 200 mg, 60 kapsula</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Минералы</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>200</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>60</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Малат магния — клеточная энергия, снижение усталости и поддержка мышц.</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Magniy malat — hujayra energiyasi, charchoqni kamaytirish va mushaklarni qoʻllab-quvvatlash.</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Malate — магний в форме малата (соли яблочной кислоты). Поддерживает выработку клеточной энергии, помогает снижать усталость и утомляемость, поддерживает мышечную функцию. Дополнительный источник магния. Халяль.</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>ECOVITA Magnesium Malate — malat (olma kislotasi tuzi) shaklidagi magniy. Hujayra energiyasi ishlab chiqarilishini qoʻllab-quvvatlaydi, charchoq va holsizlikni kamaytirishga yordam beradi, mushak funksiyasini qoʻllab-quvvatlaydi. Magniyning qoʻshimcha manbai. Halol.</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>2 капсулы содержат: магния малат — 1250 мг; элементарный магний — 200 мг; микрокристаллическая целлюлоза (носитель), желатиновая капсула</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>2 kapsula tarkibida: magniy malat — 1250 mg; elementar magniy — 200 mg; mikrokristall sellyuloza (tashuvchi), jelatin kapsulasi</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Взрослым — по 2 капсулы в день во время приёма пищи. Продолжительность приёма — 1 месяц, при необходимости курс можно повторить.</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 2 kapsula, ovqat vaqtida. Qabul muddati — 1 oy, zarur boʻlsa kursni takrorlash mumkin.</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Индивидуальная непереносимость компонентов, беременность, период лактации, возраст до 18 лет. Перед применением проконсультируйтесь с врачом. Хранить в сухом, прохладном, защищённом от прямых солнечных лучей и недоступном для детей месте при температуре не выше 25°C и относительной влажности не более 75%, в закрытой неповреждённой упаковке. Срок годности — 2 года.</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Tarkibiy qismlarga individual toʻqnashmovchilik, homiladorlik, laktatsiya davri, 18 yoshgacha. Qoʻllashdan oldin shifokor bilan maslahatlashing. Quruq, salqin, toʻgʻridan-toʻgʻri quyosh nuridan himoyalangan, bolalar yeta olmaydigan joyda, 25°C dan yuqori boʻlmagan haroratda va nisbiy namlik 75% dan oshmagan sharoitda, yopiq butun qadoqda saqlang. Yaroqlilik muddati — 2 yil.</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>images/ecovita-magnesium-malate-200.jpg</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ecovita-alpha-lipoic-acid</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ecovita-alpha-lipoic-acid-100mg-60</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ECOVITA Alpha Lipoic Acid 100 мг, 60 капсул</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ECOVITA Alpha Lipoic Acid 100 mg, 60 kapsula</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Антиоксиданты</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Пищеварение и печень</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>100</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>60</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Альфа-липоевая кислота 100 мг — антиоксидантная защита, детокс и здоровье печени.</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Alfa-lipoy kislotasi 100 mg — antioksidant himoya, detoks va jigar salomatligi.</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>ECOVITA Alpha Lipoic Acid — дополнительный источник альфа-липоевой кислоты, мощного антиоксиданта. Поддерживает детоксикацию и здоровье печени, обеспечивает антиоксидантную защиту и поддерживает здоровый метаболизм при снижении веса. Халяль.</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>ECOVITA Alpha Lipoic Acid — kuchli antioksidant boʻlgan alfa-lipoy kislotasining qoʻshimcha manbai. Detoksikatsiya va jigar salomatligini qoʻllab-quvvatlaydi, antioksidant himoyani taʼminlaydi va ozish paytida sogʻlom metabolizmni qoʻllab-quvvatlaydi. Halol.</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>1 капсула содержит: альфа-липоевая кислота — 100 мг; микрокристаллическая целлюлоза (носитель), желатиновая капсула</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>1 kapsula tarkibida: alfa-lipoy kislotasi — 100 mg; mikrokristall sellyuloza (tashuvchi), jelatin kapsulasi</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле в день во время еды или по рекомендации врача. Продолжительность приёма — 1 месяц, при необходимости курс можно повторить.</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 1 kapsula, ovqat vaqtida yoki shifokor tavsiyasiga koʻra. Qabul muddati — 1 oy, zarur boʻlsa kursni takrorlash mumkin.</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Индивидуальная непереносимость компонентов, беременность, период лактации, возраст до 18 лет. Перед применением проконсультируйтесь с врачом. Хранить в сухом, прохладном, защищённом от прямых солнечных лучей и недоступном для детей месте при температуре не выше 25°C и относительной влажности не более 75%, в закрытой неповреждённой упаковке. Срок годности — 2 года.</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Tarkibiy qismlarga individual toʻqnashmovchilik, homiladorlik, laktatsiya davri, 18 yoshgacha. Qoʻllashdan oldin shifokor bilan maslahatlashing. Quruq, salqin, toʻgʻridan-toʻgʻri quyosh nuridan himoyalangan, bolalar yeta olmaydigan joyda, 25°C dan yuqori boʻlmagan haroratda va nisbiy namlik 75% dan oshmagan sharoitda, yopiq butun qadoqda saqlang. Yaroqlilik muddati — 2 yil.</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>images/ecovita-alpha-lipoic-acid.jpg</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>опубликован</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ecovita-5-htp-b6</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ecovita-5-htp-vitamin-b6-200mg-60</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ECOVITA 5-HTP + Vitamin B6 200 мг + 2 мг, 60 капсул</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ECOVITA 5-HTP + Vitamin B6 200 mg + 2 mg, 60 kapsula</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Нервная система и сон</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Аминокислоты</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Капсулы</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>200</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>мг</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>60</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>5-гидрокситриптофан с витамином B6 — спокойствие, качество сна и выработка серотонина.</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>B6 vitaminli 5-gidroksitriptofan — xotirjamlik, uyqu sifati va serotonin ishlab chiqarilishi.</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>ECOVITA 5-HTP + Vitamin B6 — комплекс 5-гидрокситриптофана и витамина B6. Способствует спокойствию и эмоциональному комфорту, улучшению качества сна и поддерживает естественную выработку серотонина. Дополнительный источник витамина B6. Халяль.</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>ECOVITA 5-HTP + Vitamin B6 — 5-gidroksitriptofan va B6 vitamini kompleksi. Xotirjamlik va hissiy qulaylikka, uyqu sifatini yaxshilashga yordam beradi hamda serotoninning tabiiy ishlab chiqarilishini qoʻllab-quvvatlaydi. B6 vitaminining qoʻshimcha manbai. Halol.</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>2 капсулы содержат: 5-гидрокситриптофан (5-HTP) — 200 мг; витамин B6 (пиридоксина гидрохлорид) — 2 мг; микрокристаллическая целлюлоза (носитель), мальтодекстрин (носитель), диоксид кремния (антислеживатель), желатиновая капсула</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>2 kapsula tarkibida: 5-gidroksitriptofan (5-HTP) — 200 mg; vitamin B6 (piridoksin gidroxlorid) — 2 mg; mikrokristall sellyuloza (tashuvchi), maltodekstrin (tashuvchi), kremniy dioksidi (qotib qolishga qarshi), jelatin kapsulasi</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Взрослым — по 1 капсуле 2 раза в день. Продолжительность приёма — 1 месяц, при необходимости курс можно повторить.</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Kattalar uchun — kuniga 2 marta 1 tadan kapsula. Qabul muddati — 1 oy, zarur boʻlsa kursni takrorlash mumkin.</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Индивидуальная непереносимость компонентов, беременность, период лактации. Перед применением проконсультируйтесь с врачом. Хранить в сухом, прохладном, защищённом от прямых солнечных лучей и недоступном для детей месте при температуре не выше 25°C и относительной влажности не более 75%, в закрытой неповреждённой упаковке. Срок годности — 2 года.</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Tarkibiy qismlarga individual toʻqnashmovchilik, homiladorlik, laktatsiya davri. Qoʻllashdan oldin shifokor bilan maslahatlashing. Quruq, salqin, toʻgʻridan-toʻgʻri quyosh nuridan himoyalangan, bolalar yeta olmaydigan joyda, 25°C dan yuqori boʻlmagan haroratda va nisbiy namlik 75% dan oshmagan sharoitda, yopiq butun qadoqda saqlang. Yaroqlilik muddati — 2 yil.</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>ECOVITA</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>images/ecovita-5-htp-b6.jpg</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
         <is>
           <t>опубликован</t>
         </is>
@@ -25285,7 +26987,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -25295,7 +26997,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -25315,7 +27017,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -25335,7 +27037,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
